--- a/site/SEER-Medicare-Publications.xlsx
+++ b/site/SEER-Medicare-Publications.xlsx
@@ -20693,7 +20693,7 @@
     <t xml:space="preserve">Data Extraction Date</t>
   </si>
   <si>
-    <t xml:space="preserve">October 14, 2026</t>
+    <t xml:space="preserve">October 15, 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Total Publications</t>
